--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/IDAHO_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/IDAHO_2010.xlsx
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C62">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C113">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C474">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C628">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C663">
